--- a/data/trans_orig/IMC_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2007</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64396</t>
+          <t>65105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97371</t>
+          <t>100410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88666</t>
+          <t>86712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124946</t>
+          <t>123930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163087</t>
+          <t>160874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213823</t>
+          <t>209095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330745</t>
+          <t>325538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383997</t>
+          <t>379459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224651</t>
+          <t>225407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274417</t>
+          <t>275387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568864</t>
+          <t>569023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>643227</t>
+          <t>641684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>223191</t>
+          <t>224855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>272945</t>
+          <t>274872</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>285174</t>
+          <t>282943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333801</t>
+          <t>334181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>521969</t>
+          <t>519055</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>592849</t>
+          <t>593497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23851</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>31049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119829</t>
+          <t>120396</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164579</t>
+          <t>165409</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123802</t>
+          <t>123168</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169352</t>
+          <t>169656</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>253269</t>
+          <t>254450</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>318922</t>
+          <t>318140</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>417773</t>
+          <t>417413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>481677</t>
+          <t>483144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>301348</t>
+          <t>303277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>362873</t>
+          <t>361665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>739617</t>
+          <t>738791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>825627</t>
+          <t>826778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326149</t>
+          <t>326875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389061</t>
+          <t>391868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>433291</t>
+          <t>428076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493650</t>
+          <t>490117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>776136</t>
+          <t>776292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>862533</t>
+          <t>860851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>34407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89347</t>
+          <t>88443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>79553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114460</t>
+          <t>114708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144235</t>
+          <t>145037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192183</t>
+          <t>193994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>278058</t>
+          <t>276629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>331556</t>
+          <t>329595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,82 +1999,82 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>49,04%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>214214</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>193164</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>238459</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>35,21%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>517506</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>483392</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>558137</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>38,35%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>35,83%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>41,37%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>214214</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>191027</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>236804</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>31,63%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>517506</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>484845</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>553495</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>38,35%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>35,93%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>262772</t>
+          <t>263891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317320</t>
+          <t>316524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>324186</t>
+          <t>324172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>373396</t>
+          <t>374399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>602663</t>
+          <t>599045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>677388</t>
+          <t>675504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85464</t>
+          <t>85218</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121903</t>
+          <t>121797</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131235</t>
+          <t>131477</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176171</t>
+          <t>177120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>226662</t>
+          <t>225246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>283634</t>
+          <t>283690</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>391158</t>
+          <t>387597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>448907</t>
+          <t>447618</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256381</t>
+          <t>254811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>314111</t>
+          <t>311191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>661051</t>
+          <t>658769</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>745070</t>
+          <t>747126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>371572</t>
+          <t>376565</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>432284</t>
+          <t>433710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>517288</t>
+          <t>517401</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>581607</t>
+          <t>580757</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>911248</t>
+          <t>912537</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001328</t>
+          <t>1002017</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>23523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48160</t>
+          <t>47248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>51530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357630</t>
+          <t>359914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>435047</t>
+          <t>437874</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>459750</t>
+          <t>459824</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>536007</t>
+          <t>544169</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>839139</t>
+          <t>840877</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>952012</t>
+          <t>954599</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1474611</t>
+          <t>1472216</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1585898</t>
+          <t>1579551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1023027</t>
+          <t>1023184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1132522</t>
+          <t>1128316</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2525296</t>
+          <t>2530920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2682956</t>
+          <t>2679083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1245329</t>
+          <t>1245487</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1353862</t>
+          <t>1359462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1612605</t>
+          <t>1610607</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1730446</t>
+          <t>1728089</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2897465</t>
+          <t>2894168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3057593</t>
+          <t>3051497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69619</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>108081</t>
+          <t>106736</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>87751</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>129649</t>
+          <t>125838</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2012</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117137</t>
+          <t>117088</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>157817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123450</t>
+          <t>123050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163840</t>
+          <t>167237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249981</t>
+          <t>249866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>310736</t>
+          <t>309462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325575</t>
+          <t>328609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379571</t>
+          <t>379543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194895</t>
+          <t>195344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244228</t>
+          <t>241333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534907</t>
+          <t>535109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>612274</t>
+          <t>611289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175084</t>
+          <t>173138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223244</t>
+          <t>221527</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>255683</t>
+          <t>255940</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>307085</t>
+          <t>306513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>445489</t>
+          <t>437233</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>512396</t>
+          <t>512426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>37287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150694</t>
+          <t>150029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198892</t>
+          <t>197516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>198127</t>
+          <t>198699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255803</t>
+          <t>254446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>358239</t>
+          <t>358080</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>434984</t>
+          <t>431840</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>449465</t>
+          <t>448012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>514795</t>
+          <t>512195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>295884</t>
+          <t>295629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>358142</t>
+          <t>357033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>764521</t>
+          <t>763600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>856631</t>
+          <t>855501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300884</t>
+          <t>299903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>359614</t>
+          <t>364021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381732</t>
+          <t>382766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444013</t>
+          <t>448227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>702261</t>
+          <t>695050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>791114</t>
+          <t>788764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42720</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89451</t>
+          <t>88321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129268</t>
+          <t>129024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129886</t>
+          <t>130295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178426</t>
+          <t>176250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230175</t>
+          <t>230691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288062</t>
+          <t>290183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>307300</t>
+          <t>306467</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>363314</t>
+          <t>362601</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>244706</t>
+          <t>245532</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>300491</t>
+          <t>300224</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>567330</t>
+          <t>565688</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>646419</t>
+          <t>645073</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>260451</t>
+          <t>261429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>315038</t>
+          <t>317672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>277192</t>
+          <t>278482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335113</t>
+          <t>336177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>557468</t>
+          <t>557708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>636408</t>
+          <t>639573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>34684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118457</t>
+          <t>116423</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163718</t>
+          <t>162629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>172992</t>
+          <t>171650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>226177</t>
+          <t>224718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>305053</t>
+          <t>309116</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>375082</t>
+          <t>373302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>443737</t>
+          <t>439841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>501166</t>
+          <t>502636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>286154</t>
+          <t>287540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347615</t>
+          <t>349697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>741951</t>
+          <t>744464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>835604</t>
+          <t>833578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>287261</t>
+          <t>282909</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>341629</t>
+          <t>340293</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>436719</t>
+          <t>439338</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>501991</t>
+          <t>501105</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>740751</t>
+          <t>740385</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>829320</t>
+          <t>830511</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37472</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>510934</t>
+          <t>511923</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>600544</t>
+          <t>597943</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,82 +6101,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>718009</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>671912</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>768633</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>21,07%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1273311</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1209231</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1338394</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>18,81%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>17,87%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>718009</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>674353</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>771585</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>21,07%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1273311</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1213421</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1340873</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>17,93%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1581334</t>
+          <t>1577612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1701670</t>
+          <t>1698674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1077780</t>
+          <t>1079731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1186764</t>
+          <t>1190439</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2693995</t>
+          <t>2692051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2855006</t>
+          <t>2856956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1074299</t>
+          <t>1076705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1191781</t>
+          <t>1192244</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1415122</t>
+          <t>1414245</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1530209</t>
+          <t>1532204</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2523598</t>
+          <t>2515905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2688540</t>
+          <t>2681300</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21492</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42877</t>
+          <t>42907</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>67414</t>
+          <t>67382</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>103499</t>
+          <t>103740</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>96032</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>136954</t>
+          <t>137151</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2016</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109936</t>
+          <t>108859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149602</t>
+          <t>150663</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101931</t>
+          <t>101040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141537</t>
+          <t>140215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221871</t>
+          <t>223588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279181</t>
+          <t>281075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261180</t>
+          <t>258947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309831</t>
+          <t>310010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191802</t>
+          <t>190183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238031</t>
+          <t>238148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465426</t>
+          <t>463559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531772</t>
+          <t>533092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>196929</t>
+          <t>196571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244600</t>
+          <t>246443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>238917</t>
+          <t>239069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>286253</t>
+          <t>287827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451998</t>
+          <t>450984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>517359</t>
+          <t>519441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>26743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12425</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154957</t>
+          <t>152771</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205671</t>
+          <t>200575</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,82 +7471,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>20,38%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>199887</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>174496</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>225149</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>377221</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>341660</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>413447</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>19,07%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>20,9%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>199887</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>174794</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>226639</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>22,8%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>377221</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>340820</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>413372</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>380160</t>
+          <t>379446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>442622</t>
+          <t>444050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>324126</t>
+          <t>325009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>385576</t>
+          <t>389177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>718897</t>
+          <t>721317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>807593</t>
+          <t>811416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>356252</t>
+          <t>357236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417844</t>
+          <t>418924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>384931</t>
+          <t>381239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>445081</t>
+          <t>447474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>756847</t>
+          <t>751287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>848604</t>
+          <t>845506</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15405</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>34671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48273</t>
+          <t>49266</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98697</t>
+          <t>98878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140150</t>
+          <t>140699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96027</t>
+          <t>97064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137900</t>
+          <t>138160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205208</t>
+          <t>205075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262959</t>
+          <t>263666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>296377</t>
+          <t>295422</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>351969</t>
+          <t>352177</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>210937</t>
+          <t>214410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>265542</t>
+          <t>267640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>523196</t>
+          <t>526524</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>600296</t>
+          <t>599720</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>266439</t>
+          <t>268207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>321684</t>
+          <t>323871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>344444</t>
+          <t>345067</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>403632</t>
+          <t>400297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>628735</t>
+          <t>624207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>703381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32917</t>
+          <t>32115</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>42962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113051</t>
+          <t>112426</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155672</t>
+          <t>154876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>163136</t>
+          <t>162454</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>215323</t>
+          <t>212992</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>288952</t>
+          <t>284993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>352131</t>
+          <t>354596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>377997</t>
+          <t>378708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437328</t>
+          <t>442046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287012</t>
+          <t>282226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347037</t>
+          <t>344900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>686099</t>
+          <t>685473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>772044</t>
+          <t>775507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>324210</t>
+          <t>325081</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>385704</t>
+          <t>386153</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>430864</t>
+          <t>428746</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>496676</t>
+          <t>495498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>774453</t>
+          <t>773216</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>861363</t>
+          <t>864347</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29889</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38212</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>513594</t>
+          <t>512479</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>605595</t>
+          <t>601795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>580975</t>
+          <t>580496</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>676055</t>
+          <t>671696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1115808</t>
+          <t>1115134</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1246230</t>
+          <t>1244978</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1380169</t>
+          <t>1375810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1491511</t>
+          <t>1489060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1067373</t>
+          <t>1068832</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1179235</t>
+          <t>1177660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2472662</t>
+          <t>2472476</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2632485</t>
+          <t>2638614</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1196600</t>
+          <t>1203505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1308417</t>
+          <t>1313648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1451482</t>
+          <t>1452147</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1573543</t>
+          <t>1572229</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2686800</t>
+          <t>2693345</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2845348</t>
+          <t>2858270</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>20630</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>41739</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>66823</t>
+          <t>65476</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>101749</t>
+          <t>102814</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>91625</t>
+          <t>94206</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>133658</t>
+          <t>136486</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2023</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98148</t>
+          <t>98068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139014</t>
+          <t>134319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115618</t>
+          <t>114165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147066</t>
+          <t>146471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>222011</t>
+          <t>224531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273536</t>
+          <t>274670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281831</t>
+          <t>284797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>339358</t>
+          <t>339515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213949</t>
+          <t>213973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254609</t>
+          <t>253664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509540</t>
+          <t>511334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577076</t>
+          <t>577299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154072</t>
+          <t>153052</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202452</t>
+          <t>200050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>250706</t>
+          <t>248329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>292002</t>
+          <t>292578</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>414068</t>
+          <t>415538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>478186</t>
+          <t>479757</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>41517</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52415</t>
+          <t>56472</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183531</t>
+          <t>186527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>718536</t>
+          <t>800307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123589</t>
+          <t>123114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>160173</t>
+          <t>158523</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322412</t>
+          <t>322286</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1007858</t>
+          <t>1045621</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>233479</t>
+          <t>197787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>509567</t>
+          <t>510011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>307494</t>
+          <t>310321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>356487</t>
+          <t>360901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>507410</t>
+          <t>503584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>837270</t>
+          <t>834038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>215874</t>
+          <t>192156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507706</t>
+          <t>499582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401577</t>
+          <t>403252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>453515</t>
+          <t>453575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560409</t>
+          <t>539910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934175</t>
+          <t>942026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42249</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>104439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146924</t>
+          <t>149881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132462</t>
+          <t>132659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615090</t>
+          <t>577107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256669</t>
+          <t>255890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>841792</t>
+          <t>882643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>278462</t>
+          <t>276780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>334717</t>
+          <t>337679</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99980</t>
+          <t>116073</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>296136</t>
+          <t>299417</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>344094</t>
+          <t>318503</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>623383</t>
+          <t>622357</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>224988</t>
+          <t>224645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>285181</t>
+          <t>284748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155784</t>
+          <t>175449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>437006</t>
+          <t>435638</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369224</t>
+          <t>376179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>682549</t>
+          <t>682434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47215</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130093</t>
+          <t>126887</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175463</t>
+          <t>175694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>137614</t>
+          <t>136159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198838</t>
+          <t>199138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>287804</t>
+          <t>281460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>364309</t>
+          <t>360349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>375297</t>
+          <t>372662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437775</t>
+          <t>440351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>328164</t>
+          <t>326268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>521968</t>
+          <t>513680</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>725338</t>
+          <t>725627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>930721</t>
+          <t>910126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>303224</t>
+          <t>299768</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366181</t>
+          <t>367578</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>367028</t>
+          <t>368852</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>509754</t>
+          <t>512177</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>715019</t>
+          <t>709761</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>858642</t>
+          <t>855734</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>34042</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43770</t>
+          <t>45177</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>572434</t>
+          <t>572483</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1386751</t>
+          <t>1419118</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>572598</t>
+          <t>574999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1266235</t>
+          <t>1191380</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1184003</t>
+          <t>1182078</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2312851</t>
+          <t>2336983</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1075471</t>
+          <t>1108416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1545069</t>
+          <t>1550430</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>969394</t>
+          <t>974811</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1307788</t>
+          <t>1300710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2250623</t>
+          <t>2230109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2794816</t>
+          <t>2797040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>875192</t>
+          <t>878055</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1269069</t>
+          <t>1266779</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1210335</t>
+          <t>1227877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1622360</t>
+          <t>1613345</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2290506</t>
+          <t>2243364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2842631</t>
+          <t>2829906</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67463</t>
+          <t>64894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>58107</t>
+          <t>56378</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99566</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>89405</t>
+          <t>85155</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>151039</t>
+          <t>144382</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65105</t>
+          <t>64801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>97936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86712</t>
+          <t>88176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123930</t>
+          <t>123553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160874</t>
+          <t>162038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209095</t>
+          <t>211844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325538</t>
+          <t>329668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379459</t>
+          <t>379783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225407</t>
+          <t>225965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275387</t>
+          <t>274885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569023</t>
+          <t>567021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>641684</t>
+          <t>640988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224855</t>
+          <t>225248</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>274872</t>
+          <t>276561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>282943</t>
+          <t>282546</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>334181</t>
+          <t>332703</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>519055</t>
+          <t>523917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593497</t>
+          <t>595486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31049</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120396</t>
+          <t>118435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>165409</t>
+          <t>165302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123168</t>
+          <t>123746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169656</t>
+          <t>168503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254450</t>
+          <t>253410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>318140</t>
+          <t>316852</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>417413</t>
+          <t>419695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>483144</t>
+          <t>483387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>303277</t>
+          <t>299744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>361665</t>
+          <t>359526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>738791</t>
+          <t>737417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>826778</t>
+          <t>827252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326875</t>
+          <t>325155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>391868</t>
+          <t>388077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>428076</t>
+          <t>432506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490117</t>
+          <t>493484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>776292</t>
+          <t>775368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860851</t>
+          <t>866737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30758</t>
+          <t>30467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>15760</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34407</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55186</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88443</t>
+          <t>90912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79553</t>
+          <t>78923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114708</t>
+          <t>113944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145037</t>
+          <t>146256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193994</t>
+          <t>193890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>276629</t>
+          <t>277980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>329595</t>
+          <t>330636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>193164</t>
+          <t>189759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>238459</t>
+          <t>240628</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>483392</t>
+          <t>480129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>558137</t>
+          <t>552041</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>263891</t>
+          <t>262551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>316524</t>
+          <t>315932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>324172</t>
+          <t>321800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>374399</t>
+          <t>373284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>599045</t>
+          <t>603969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>675504</t>
+          <t>679148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34173</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85218</t>
+          <t>84030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121797</t>
+          <t>120997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131477</t>
+          <t>129483</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177120</t>
+          <t>174285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>225246</t>
+          <t>224494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>283690</t>
+          <t>283396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>387597</t>
+          <t>388395</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>447618</t>
+          <t>447309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254811</t>
+          <t>252525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311191</t>
+          <t>312303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>658769</t>
+          <t>658549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>747126</t>
+          <t>741639</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>376565</t>
+          <t>375109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>433710</t>
+          <t>435438</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>517401</t>
+          <t>522096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>580757</t>
+          <t>586019</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>912537</t>
+          <t>911854</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1002017</t>
+          <t>999266</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47248</t>
+          <t>46993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>28405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51530</t>
+          <t>53644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>359914</t>
+          <t>359204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>437874</t>
+          <t>432962</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>459824</t>
+          <t>460185</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>544169</t>
+          <t>542817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>840877</t>
+          <t>838073</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>954599</t>
+          <t>949602</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1472216</t>
+          <t>1472692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1579551</t>
+          <t>1587361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1023184</t>
+          <t>1023298</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1128316</t>
+          <t>1128583</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2530920</t>
+          <t>2526228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2679083</t>
+          <t>2690112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1245487</t>
+          <t>1246114</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1359462</t>
+          <t>1358303</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1610607</t>
+          <t>1617218</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1728089</t>
+          <t>1727964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2894168</t>
+          <t>2885137</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3051497</t>
+          <t>3048522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29049</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69404</t>
+          <t>70946</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106736</t>
+          <t>107350</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>87751</t>
+          <t>87153</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125838</t>
+          <t>126746</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117088</t>
+          <t>115874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157817</t>
+          <t>157146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123050</t>
+          <t>123146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167237</t>
+          <t>164393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249866</t>
+          <t>251638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309462</t>
+          <t>313247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>328609</t>
+          <t>327006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379543</t>
+          <t>381097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195344</t>
+          <t>195405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241333</t>
+          <t>244065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535109</t>
+          <t>534506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611289</t>
+          <t>609684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173138</t>
+          <t>174129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221527</t>
+          <t>222674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>255940</t>
+          <t>255900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>306513</t>
+          <t>308489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>437233</t>
+          <t>448375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>512426</t>
+          <t>519243</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13328</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>36263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150029</t>
+          <t>150902</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>197516</t>
+          <t>202721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>198699</t>
+          <t>198963</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254446</t>
+          <t>250921</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,47 +4429,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>20,12%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>398031</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>361600</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>433614</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>20,09%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>398031</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>358080</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>431840</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>448012</t>
+          <t>452233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>512195</t>
+          <t>517822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>295629</t>
+          <t>298523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>357033</t>
+          <t>355612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>763600</t>
+          <t>762856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>855501</t>
+          <t>852902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299903</t>
+          <t>298773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>364021</t>
+          <t>361334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382766</t>
+          <t>382659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448227</t>
+          <t>448117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>695050</t>
+          <t>699029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>788764</t>
+          <t>790907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33644</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42720</t>
+          <t>41304</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88321</t>
+          <t>89017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129024</t>
+          <t>130691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130295</t>
+          <t>129827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176250</t>
+          <t>176401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,47 +4998,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>259611</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>230880</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>291567</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>17,48%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>259611</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>230691</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>290183</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>306467</t>
+          <t>305813</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>362601</t>
+          <t>365049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>245532</t>
+          <t>244090</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>300224</t>
+          <t>298358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>565688</t>
+          <t>564949</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>645073</t>
+          <t>646764</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>261429</t>
+          <t>262107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317672</t>
+          <t>319485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>278482</t>
+          <t>277902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>336177</t>
+          <t>336380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>557708</t>
+          <t>556655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>639573</t>
+          <t>632915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116423</t>
+          <t>115281</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162629</t>
+          <t>163617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>171650</t>
+          <t>173698</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>224718</t>
+          <t>225861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>309116</t>
+          <t>302810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>373302</t>
+          <t>372442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439841</t>
+          <t>438726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>502636</t>
+          <t>501889</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287540</t>
+          <t>285707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349697</t>
+          <t>345230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>744464</t>
+          <t>743949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>833578</t>
+          <t>834134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>282909</t>
+          <t>284900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>340293</t>
+          <t>344113</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>439338</t>
+          <t>440879</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>501105</t>
+          <t>503105</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>740385</t>
+          <t>741002</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>830511</t>
+          <t>826481</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>38074</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26248</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51175</t>
+          <t>49568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>511923</t>
+          <t>514594</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>597943</t>
+          <t>602330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>671912</t>
+          <t>668583</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>768633</t>
+          <t>769102</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1209231</t>
+          <t>1205829</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1338394</t>
+          <t>1342006</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1577612</t>
+          <t>1580954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1698674</t>
+          <t>1702513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1079731</t>
+          <t>1072948</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1190439</t>
+          <t>1190830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2692051</t>
+          <t>2695287</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2856956</t>
+          <t>2858150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1076705</t>
+          <t>1072961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1192244</t>
+          <t>1183026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1414245</t>
+          <t>1412103</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1532204</t>
+          <t>1530271</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2515905</t>
+          <t>2524117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2681300</t>
+          <t>2691340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21492</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42907</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>68543</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>103740</t>
+          <t>104018</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>95867</t>
+          <t>95137</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137151</t>
+          <t>137223</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108859</t>
+          <t>109325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150663</t>
+          <t>152419</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101040</t>
+          <t>101566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140215</t>
+          <t>140327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223588</t>
+          <t>226522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>281582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258947</t>
+          <t>259348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310010</t>
+          <t>310875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>190183</t>
+          <t>190882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238148</t>
+          <t>237856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463559</t>
+          <t>464547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533092</t>
+          <t>533779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>196571</t>
+          <t>196568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>246443</t>
+          <t>244572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>239069</t>
+          <t>240678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287827</t>
+          <t>288929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>450984</t>
+          <t>451923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>519441</t>
+          <t>517904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30603</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>152771</t>
+          <t>155076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>200575</t>
+          <t>205446</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>174496</t>
+          <t>174067</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>225149</t>
+          <t>230232</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341660</t>
+          <t>342423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>413447</t>
+          <t>414332</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>379446</t>
+          <t>378861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>444050</t>
+          <t>439702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>325009</t>
+          <t>324591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>389177</t>
+          <t>384764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>721317</t>
+          <t>719119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>811416</t>
+          <t>807559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>357236</t>
+          <t>357911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418924</t>
+          <t>417006</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381239</t>
+          <t>385925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447474</t>
+          <t>447534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>751287</t>
+          <t>756406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>845506</t>
+          <t>846941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34671</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>25647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49266</t>
+          <t>50024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98878</t>
+          <t>98022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140699</t>
+          <t>138680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97064</t>
+          <t>96249</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138160</t>
+          <t>136519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205075</t>
+          <t>203906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263666</t>
+          <t>265822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>295422</t>
+          <t>297919</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>352177</t>
+          <t>352573</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>214410</t>
+          <t>214351</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>267640</t>
+          <t>266609</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>526524</t>
+          <t>526577</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>599720</t>
+          <t>603074</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>268207</t>
+          <t>267429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>323871</t>
+          <t>325498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>345067</t>
+          <t>343836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>400297</t>
+          <t>400876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>624207</t>
+          <t>628100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>703381</t>
+          <t>703632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>112426</t>
+          <t>113684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154876</t>
+          <t>156033</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162454</t>
+          <t>161485</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212992</t>
+          <t>215620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284993</t>
+          <t>285419</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>354596</t>
+          <t>353212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>378708</t>
+          <t>379278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>442046</t>
+          <t>441530</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>282226</t>
+          <t>284694</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344900</t>
+          <t>345334</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>685473</t>
+          <t>686110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>775507</t>
+          <t>771763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>325081</t>
+          <t>323167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>386153</t>
+          <t>383831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>428746</t>
+          <t>434779</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>495498</t>
+          <t>495729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>773216</t>
+          <t>771620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>864347</t>
+          <t>857468</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29043</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37706</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>512479</t>
+          <t>515003</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>601795</t>
+          <t>601102</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>580496</t>
+          <t>578055</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>671696</t>
+          <t>667457</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1115134</t>
+          <t>1116859</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1244978</t>
+          <t>1245995</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1375810</t>
+          <t>1369320</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1489060</t>
+          <t>1489497</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1068832</t>
+          <t>1062071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1177660</t>
+          <t>1174990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2472476</t>
+          <t>2471593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2638614</t>
+          <t>2626506</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1203505</t>
+          <t>1197557</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1313648</t>
+          <t>1314035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1452147</t>
+          <t>1456867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1572229</t>
+          <t>1570569</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2693345</t>
+          <t>2691702</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2858270</t>
+          <t>2848614</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20630</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65476</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>100931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>94206</t>
+          <t>92853</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>136486</t>
+          <t>133934</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>116128</t>
+          <t>123787</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98068</t>
+          <t>107319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134319</t>
+          <t>145717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>130232</t>
+          <t>137755</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114165</t>
+          <t>123295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146471</t>
+          <t>157157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>246360</t>
+          <t>261542</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224531</t>
+          <t>235548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>274670</t>
+          <t>289961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311334</t>
+          <t>327829</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284797</t>
+          <t>301433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>339515</t>
+          <t>355421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>232273</t>
+          <t>252455</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213973</t>
+          <t>230373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253664</t>
+          <t>271427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>543607</t>
+          <t>580284</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511334</t>
+          <t>541744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577299</t>
+          <t>617462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>176556</t>
+          <t>202908</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153052</t>
+          <t>178927</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>200050</t>
+          <t>228660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>271205</t>
+          <t>294643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>248329</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>292578</t>
+          <t>317526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>447761</t>
+          <t>497551</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>415538</t>
+          <t>463396</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>479757</t>
+          <t>531839</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>30523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,17 +10333,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27929</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56472</t>
+          <t>46028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>620540</t>
+          <t>668011</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>620540</t>
+          <t>668011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>620540</t>
+          <t>668011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>645117</t>
+          <t>697196</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>645117</t>
+          <t>697196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>645117</t>
+          <t>697196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1265657</t>
+          <t>1365207</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1265657</t>
+          <t>1365207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1265657</t>
+          <t>1365207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>398460</t>
+          <t>165515</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186527</t>
+          <t>139112</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>800307</t>
+          <t>191839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>139384</t>
+          <t>156145</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123114</t>
+          <t>139217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158523</t>
+          <t>178961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>537844</t>
+          <t>321659</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322286</t>
+          <t>290236</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1045621</t>
+          <t>354995</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>393316</t>
+          <t>440308</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197787</t>
+          <t>405926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>510011</t>
+          <t>474874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>334429</t>
+          <t>379814</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>310321</t>
+          <t>352434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>360901</t>
+          <t>405694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>727745</t>
+          <t>820122</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>503584</t>
+          <t>778464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>834038</t>
+          <t>868577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>389205</t>
+          <t>430625</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192156</t>
+          <t>396141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499582</t>
+          <t>470045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>426795</t>
+          <t>472612</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>403252</t>
+          <t>443950</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>453575</t>
+          <t>501708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>816000</t>
+          <t>903236</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>539910</t>
+          <t>855071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>942026</t>
+          <t>948017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26938</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43065</t>
+          <t>42921</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1182173</t>
+          <t>1037531</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1182173</t>
+          <t>1037531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1182173</t>
+          <t>1037531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>927546</t>
+          <t>1037451</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>927546</t>
+          <t>1037451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>927546</t>
+          <t>1037451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2109719</t>
+          <t>2074982</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2109719</t>
+          <t>2074982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2109719</t>
+          <t>2074982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>125067</t>
+          <t>137707</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104439</t>
+          <t>117666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>149881</t>
+          <t>162508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>311619</t>
+          <t>127484</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132659</t>
+          <t>109048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577107</t>
+          <t>149153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>436686</t>
+          <t>265191</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255890</t>
+          <t>236548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>882643</t>
+          <t>293055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>307444</t>
+          <t>357681</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>276780</t>
+          <t>325428</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>337679</t>
+          <t>390542</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>222646</t>
+          <t>263541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116073</t>
+          <t>240039</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>299417</t>
+          <t>288391</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>530090</t>
+          <t>621222</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>318503</t>
+          <t>580356</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>622357</t>
+          <t>663190</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>252661</t>
+          <t>281718</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>224645</t>
+          <t>249788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>284748</t>
+          <t>312304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>327614</t>
+          <t>378929</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175449</t>
+          <t>351834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>435638</t>
+          <t>405874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>580274</t>
+          <t>660647</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376179</t>
+          <t>616744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>682434</t>
+          <t>700702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>26996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>46602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>696878</t>
+          <t>788143</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>696878</t>
+          <t>788143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>696878</t>
+          <t>788143</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>878067</t>
+          <t>787562</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>878067</t>
+          <t>787562</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>878067</t>
+          <t>787562</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1574945</t>
+          <t>1575705</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1574945</t>
+          <t>1575705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1574945</t>
+          <t>1575705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>150066</t>
+          <t>160295</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126887</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175694</t>
+          <t>185676</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>176596</t>
+          <t>196470</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>136159</t>
+          <t>173793</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>199138</t>
+          <t>217605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>326662</t>
+          <t>356766</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>281460</t>
+          <t>327547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>360349</t>
+          <t>391199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>406268</t>
+          <t>425249</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>372662</t>
+          <t>392247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>440351</t>
+          <t>461984</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>381840</t>
+          <t>340591</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326268</t>
+          <t>314588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>513680</t>
+          <t>367653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>788109</t>
+          <t>765840</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>725627</t>
+          <t>723449</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>910126</t>
+          <t>805542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>334750</t>
+          <t>365461</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>299768</t>
+          <t>333835</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367578</t>
+          <t>401312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>468741</t>
+          <t>508889</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>368852</t>
+          <t>478115</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>512177</t>
+          <t>536336</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>803492</t>
+          <t>874350</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>709761</t>
+          <t>830991</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>855734</t>
+          <t>917967</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45177</t>
+          <t>46524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>898647</t>
+          <t>958630</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>898647</t>
+          <t>958630</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>898647</t>
+          <t>958630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1049448</t>
+          <t>1070077</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1049448</t>
+          <t>1070077</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1049448</t>
+          <t>1070077</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1948096</t>
+          <t>2028707</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1948096</t>
+          <t>2028707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1948096</t>
+          <t>2028707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>789721</t>
+          <t>587304</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>572483</t>
+          <t>541960</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1419118</t>
+          <t>637416</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>757830</t>
+          <t>617853</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>574999</t>
+          <t>578618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1191380</t>
+          <t>655984</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1547552</t>
+          <t>1205157</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1182078</t>
+          <t>1143450</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2336983</t>
+          <t>1264485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1418361</t>
+          <t>1551067</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1108416</t>
+          <t>1485392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1550430</t>
+          <t>1613695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1171189</t>
+          <t>1236402</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>974811</t>
+          <t>1185862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1300710</t>
+          <t>1281565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2589550</t>
+          <t>2787469</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2230109</t>
+          <t>2701455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2797040</t>
+          <t>2865383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1153171</t>
+          <t>1280712</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>878055</t>
+          <t>1217416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1266779</t>
+          <t>1343484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1494356</t>
+          <t>1655073</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1227877</t>
+          <t>1601917</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1613345</t>
+          <t>1709468</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2647527</t>
+          <t>2935784</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2243364</t>
+          <t>2850937</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2829906</t>
+          <t>3018013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>36984</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>19228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>64894</t>
+          <t>52969</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>76803</t>
+          <t>82958</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56378</t>
+          <t>64843</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,17 +12644,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>113787</t>
+          <t>116191</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>85155</t>
+          <t>92099</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>144382</t>
+          <t>143057</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
